--- a/AAII_Financials/Quarterly/RNR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RNR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
   <si>
     <t>RNR</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2775900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2203900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2988500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3197300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3197900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3477800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2341800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3957000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2837300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2635100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3227900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1861900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1866700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2219600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2011200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1286100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>910400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>898300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1406700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1544200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2355600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>890200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1373900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1309400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2444000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>897400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1101500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1054300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2029400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>806200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>544800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>626700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>897400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>413400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>489600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>633100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>962300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>465400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>354400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>460100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1505700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1505800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1552200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1538500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1684700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3391200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2161900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2064000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1953900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1797000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1574000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1287300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1353800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1233500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>413200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>417600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>361200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>376500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>334000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>328000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>552800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>267200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>238300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>215200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>444200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>210600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>208600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>202200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>351400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>124000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>120500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>109800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>202800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>97700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>98600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>76800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>171500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>83300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>74100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>80600</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1270300</v>
+      </c>
+      <c r="E10" s="3">
         <v>698100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1436300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1658800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1513200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>86600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>179900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1893000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>883400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>838100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1653900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>574600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>513000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>986100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1598000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>868500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>549200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>521800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1072700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1216200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1802800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>623000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1135600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1094200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1999800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>686800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>892900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>852100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1678000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>682200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>424300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>516900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>694600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>315700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>391000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>556300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>790800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>382100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>280300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>379500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,50 +1496,53 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>-5400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2000</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>-45900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>17300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>20300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>61700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1532,8 +1552,8 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1601,8 +1621,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1610,32 +1633,32 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>64600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>225600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>10000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1663,8 +1686,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>8</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>8</v>
@@ -1681,21 +1704,21 @@
       <c r="AB15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC15" s="3">
-        <v>200</v>
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD15" s="3">
         <v>200</v>
       </c>
       <c r="AE15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF15" s="3">
         <v>500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>200</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1705,8 +1728,8 @@
       <c r="AJ15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK15" s="3">
-        <v>0</v>
+      <c r="AK15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1619100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1614300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1683100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1687000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1832200</v>
-      </c>
       <c r="H17" s="3">
+        <v>1834200</v>
+      </c>
+      <c r="I17" s="3">
         <v>3514200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2399200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2215300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2079800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1922200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1721100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1383800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1446300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1323800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1319400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2460500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1152300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1298600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1075100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2195300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2073900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1200000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1201800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1254300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1669900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>865000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1053100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>924200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1199700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>434900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>669100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>567700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>528500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>317400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>436100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1345400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>606200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>328900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>259900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>245200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1156900</v>
+      </c>
+      <c r="E18" s="3">
         <v>589600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1305400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1510300</v>
       </c>
-      <c r="G18" s="3">
-        <v>1365700</v>
-      </c>
       <c r="H18" s="3">
+        <v>1363700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-36400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-57400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1741700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>757500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>712900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1506800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>478100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>420400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>895800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>691800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1174400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-241900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-400300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>331600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-651100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>281700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-309800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>172100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>55100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>774100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>32400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>48400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>130100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>829700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>371300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-124300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>59000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>368900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>96000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>53500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-712300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>356100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>136500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>94500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>214900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,175 +2085,179 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E20" s="3">
         <v>9000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>15700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>48400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-16800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>35700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-12400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>25900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>13500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>19300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-43400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-21900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-12900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-16400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-28300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>21400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>22900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>17900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>4600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>15400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>6700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-400</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1149500</v>
+      </c>
+      <c r="E21" s="3">
         <v>580600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1354300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1512000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1379800</v>
-      </c>
       <c r="H21" s="3">
+        <v>1377800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-40000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-98900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1984100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>758600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>693300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1519200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>452200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>406900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>881300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2239,65 +2276,68 @@
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-336400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>203600</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD21" s="3">
         <v>53100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>127800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>847800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>373300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-151900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>68200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>393400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>114300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>67900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-703600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>383000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>149500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>105000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>204600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2305,100 +2345,100 @@
         <v>31800</v>
       </c>
       <c r="E22" s="3">
+        <v>31800</v>
+      </c>
+      <c r="F22" s="3">
         <v>31400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>31800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>23200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>23800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>23100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>23000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>11900</v>
       </c>
       <c r="V22" s="3">
         <v>11900</v>
       </c>
       <c r="W22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="X22" s="3">
         <v>23700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>11900</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>11800</v>
       </c>
       <c r="Z22" s="3">
         <v>11800</v>
       </c>
       <c r="AA22" s="3">
+        <v>11800</v>
+      </c>
+      <c r="AB22" s="3">
         <v>26800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>14900</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>16200</v>
       </c>
       <c r="AD22" s="3">
         <v>16200</v>
       </c>
       <c r="AE22" s="3">
+        <v>16200</v>
+      </c>
+      <c r="AF22" s="3">
         <v>28600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>12500</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>11800</v>
       </c>
       <c r="AH22" s="3">
         <v>11800</v>
       </c>
       <c r="AI22" s="3">
+        <v>11800</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>23500</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>11800</v>
       </c>
       <c r="AK22" s="3">
         <v>11800</v>
@@ -2407,10 +2447,10 @@
         <v>11800</v>
       </c>
       <c r="AM22" s="3">
+        <v>11800</v>
+      </c>
+      <c r="AN22" s="3">
         <v>20600</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>10500</v>
       </c>
       <c r="AO22" s="3">
         <v>10500</v>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>10500</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>10500</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1117700</v>
+      </c>
+      <c r="E23" s="3">
         <v>548800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1263700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1480600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1340600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-70800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-83100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1734700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>707800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>633800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1434300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>425800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>380700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>869200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>698700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1186100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-297300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-434200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>306900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-662500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>241500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-350000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>181700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>66100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>748100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>16300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>36900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>111600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>819000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>360700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-132800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>50300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>345200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>88800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>43400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-722500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>350900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>132600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>83600</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>186700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>139400</v>
+      </c>
+      <c r="E24" s="3">
         <v>33000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>116100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>148900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>176900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-45500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-63900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>102000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-20800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-554200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-30500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-36700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>18600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-23600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-5700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-19500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>21000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>17000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-8900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>3100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-19000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>4200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-7700</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>978300</v>
+      </c>
+      <c r="E26" s="3">
         <v>515800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1147600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1331700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1163700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-19200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1632700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>728600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>618500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1988500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>416500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>374800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>840300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>693300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1188900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-266700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-397500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>288300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-638900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>247200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-330500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>191600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>74400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>727000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>25200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>40300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>107900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>802000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>353100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-124000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>48800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>344100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>92200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>40300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-703500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>346600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>132300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>91300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>188100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>643200</v>
+      </c>
+      <c r="E27" s="3">
         <v>280000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>739100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>892600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>813200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>158800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-195900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1155800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>487700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>359500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1553500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>191400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>188100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>555200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>447800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-825700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-325200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-394600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>210700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-450500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>165600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-287000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>187500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>47200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>487800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-80500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>33300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>36300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>633900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>270600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-83100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>32400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>245800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>56300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>34500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-504900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>263300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>91400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>68700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>145100</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3209,8 +3270,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -3227,12 +3288,12 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>8800</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3254,12 +3315,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-38100</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-15700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-48400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>16800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-35700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>12400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-25900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-13500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-19300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>43400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>21900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>12900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>16400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>28300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-21400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-22900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-4600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-15400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-6700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>400</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>663100</v>
+      </c>
+      <c r="E33" s="3">
         <v>293400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>760500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>916500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>835400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>170000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-189700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1182500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>503900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>373600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1585500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>202800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>199900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>572900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>447800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-825700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-325200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-394600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>210700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-450500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>165600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-287000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>187500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>47200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>487800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-71700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>33300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>36300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>633900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>270600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-83100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>32400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>245800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>56300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-504900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>263300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>91400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>68700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>145100</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>663100</v>
+      </c>
+      <c r="E35" s="3">
         <v>293400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>760500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>916500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>835400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>170000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-189700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1182500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>503900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>373600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1585500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>202800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>199900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>572900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>447800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-825700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-325200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-394600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>210700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-450500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>165600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-287000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>187500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>47200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>487800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-71700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>33300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>36300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>633900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>270600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-83100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>32400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>245800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>56300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-504900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>263300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>91400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>68700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>145100</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,175 +4305,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1302200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1562900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1731200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1701600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1428700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1632800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1676600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1572900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1627100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1606700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1877500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1195900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>943900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1063700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1194300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1204200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1398100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1563100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1859000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1440700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1789800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1286700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1736800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1287400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1185800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>896200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1379100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>871300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>670600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1021300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1107900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>453000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>548500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>648000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1361600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>581600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>623200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>454100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>421200</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>493300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>29142400</v>
+      </c>
+      <c r="E42" s="3">
         <v>28792000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>29651600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>29797800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>29004100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>28365900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>28098400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>28598200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26467200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>25950500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>25494300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>22609100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>22262900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>19876600</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4463,130 +4553,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8574700</v>
+      </c>
+      <c r="E43" s="3">
         <v>8280400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7667000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8185100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9386700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8598500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7381900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8559000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9351300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9599600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7902900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6409500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6999800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6200900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5490000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5777700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5687700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5338200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4162000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4464500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4939000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4769300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3462900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4090100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4168400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3447200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2678300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3025100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3536500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3164300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1793600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2193200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2465600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1796100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1407800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1715000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1704200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1600200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1093200</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1374400</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,53 +4803,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4136000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4028600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4144500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4328700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4568300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4818700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4752000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5043600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5095200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5198100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5583800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4421400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4862700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4859800</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>44723000</v>
+      </c>
+      <c r="E46" s="3">
         <v>44018700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>44188000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>45229900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>45803400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>44629700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>42797200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>44971300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>43974900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>43637900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>41783300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35664800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36256500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>33131900</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,174 +5053,180 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7078700</v>
+      </c>
+      <c r="E47" s="3">
         <v>6386600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6429100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6013800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5501100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5228700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4545300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4348900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3978800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3590500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3637300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3265500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3174200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3236800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>22220400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>20893200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>20597800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>20851200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>21442700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>20866400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>20065100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>20373900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>20558200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>20319300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>19723600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>17818600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>17368800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>16947900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>16388300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>14852800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>11885700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>11545700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>10710700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>10221700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>9503400</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>9642200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>9408900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>9459900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>9317000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>9214600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3">
         <v>112700</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
         <v>99900</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3">
         <v>89500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -5150,29 +5258,29 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD48" s="3">
         <v>62600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>40800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>39300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>40900</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI48" s="3">
-        <v>0</v>
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ48" s="3">
         <v>0</v>
@@ -5195,130 +5303,136 @@
       <c r="AP48" s="3">
         <v>0</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2308600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2283400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2171600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2307400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2401000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2371000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2256500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2436600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2553100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2581000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2526800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1501000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1536200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1478900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>237800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>239200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>240600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>242100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>243500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>245000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>246600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>248100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>249600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>257400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>258600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>260100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>262200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>263300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>265200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>267200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>237400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>238800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>240200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>241600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>243100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>244800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>246400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>248300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>251200</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>254700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,61 +5678,64 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>392200</v>
+      </c>
+      <c r="E52" s="3">
         <v>323900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>197000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>241500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>322300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>639300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>307600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>254400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>261100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>367900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>187500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>312900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>333000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>322800</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -5683,8 +5803,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>55195600</v>
+      </c>
+      <c r="E54" s="3">
         <v>53718300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>53800400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>54498100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>54727500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>53633400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>50707600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>52756400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>51567600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>50944300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>49007100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>40843100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41399900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>38270300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>36552900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35935800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35034400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>34848100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33959500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33536300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32726800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32236100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>30820600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>30995800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30479800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>27465500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>26330100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>25644200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>26087000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>24559600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>18676200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>17096400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>17023400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>15922200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>15226100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>15044900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>13705700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>13319600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>12352100</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>12659500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,53 +6145,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25875600</v>
+      </c>
+      <c r="E57" s="3">
         <v>25421600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8250300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>25714900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>26453800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26266100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24258600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>25007100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24906800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>25151400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24334700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20090300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20466500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20375900</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6137,53 +6268,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>28500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>49900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>529200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>456000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>65900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>81900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>80800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>748000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3500</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6259,175 +6393,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7201100</v>
+      </c>
+      <c r="E59" s="3">
         <v>6899600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6061100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6991100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7572400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7013600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6020100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7103900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7705500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7258100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6160400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5250900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5730200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5263800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8981200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9794600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10020800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9773900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8562700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8721800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9569300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9221600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7384500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8789900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8902800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7657400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5629800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6553700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7216400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6898300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3998400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4585300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4843100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4027400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2675400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3125100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3307000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3173400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2211300</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2646600</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33085900</v>
+      </c>
+      <c r="E60" s="3">
         <v>32323900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14340000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32706500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34076100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33808900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30734700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32176900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32694200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32409600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30575800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26089300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26198800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25643200</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,175 +6643,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2330900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2330100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2456700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2229100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2228400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2228800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1572200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1885900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1885200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1884400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2009100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1142000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1882100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1141000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1170400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1169900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1169400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1168900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1168400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1137800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1137300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1136800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1136300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1135700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1135200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1134700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1409200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1408800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1408400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1217200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>991100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>990700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>990400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>990000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>989600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>989200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>988900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>945700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>948700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>951600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>615300</v>
+      </c>
+      <c r="E62" s="3">
         <v>507100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>17793000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>591100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>580300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>557100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>849000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>590000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>474000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>559600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>866500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>360900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>239900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>263300</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6747,8 +6893,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>36032100</v>
+      </c>
+      <c r="E66" s="3">
         <v>35161000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>34589600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35526600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36884700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36594700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33155800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34652800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35053400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>34853600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33451300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27592200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28320800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>27047400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>31227600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>31054000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29295700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28731100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>27335200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26786800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>25509100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>25157800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23260300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23605000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23132600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21782000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>20358700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19693000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>20174100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19005600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13631100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12209900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12163300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>11485900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>10834800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>10641900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>8750400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>8458800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>7485500</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7851700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7586,7 +7754,7 @@
         <v>750000</v>
       </c>
       <c r="W70" s="3">
-        <v>525000</v>
+        <v>750000</v>
       </c>
       <c r="X70" s="3">
         <v>525000</v>
@@ -7604,7 +7772,7 @@
         <v>525000</v>
       </c>
       <c r="AC70" s="3">
-        <v>650000</v>
+        <v>525000</v>
       </c>
       <c r="AD70" s="3">
         <v>650000</v>
@@ -7625,7 +7793,7 @@
         <v>650000</v>
       </c>
       <c r="AJ70" s="3">
-        <v>400000</v>
+        <v>650000</v>
       </c>
       <c r="AK70" s="3">
         <v>400000</v>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>400000</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>400000</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11041400</v>
+      </c>
+      <c r="E72" s="3">
         <v>10733400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10827300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10114200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9225100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8417800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8276200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8494600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7341000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6866300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6522000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4965200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4790500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4618800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4071400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3639400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4480900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4822000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5232600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5037800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5504800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5065100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5373900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5201800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5171700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4613500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4710900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4691900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4670300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4317500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4058200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4155300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4135800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>3957300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3913800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3930000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4447500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4289200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4207700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4151000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11070200</v>
+      </c>
+      <c r="E76" s="3">
         <v>10764200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10858700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10752400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10049700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9598500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9824000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10492600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9428900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9042800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8705000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6838600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6652800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5115500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4575300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4131900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4988700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5367000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5874300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5999500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6692600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6553300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7035200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6865800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6822200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5158500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5321400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5301200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5262800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4904000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4395100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4236500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4210100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4036300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3991400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4003000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4555300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4460800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4466600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4407800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>663100</v>
+      </c>
+      <c r="E81" s="3">
         <v>293400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>760500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>916500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>835400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>170000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-189700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1182500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>503900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>373600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1585500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>202800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>199900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>572900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>447800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-825700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-325200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-394600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>210700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-450500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>165600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-287000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>187500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>47200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>487800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-71700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>33300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>36300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>633900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>270600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-83100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>32400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>245800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>56300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-504900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>263300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>91400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>68700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>145100</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,58 +8990,59 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E83" s="3">
         <v>3700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>225600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-13700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-47800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-40300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-32900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-25700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-10800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>18900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -8854,15 +9053,15 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1700</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>8</v>
       </c>
@@ -8878,44 +9077,47 @@
       <c r="AD83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH83" s="3">
         <v>-30800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>6200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>24700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>13700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>12700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>7100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>11500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>6400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>11000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>852400</v>
+      </c>
+      <c r="E89" s="3">
         <v>687600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>483000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1582800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1469600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>157800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>778900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1490100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1212300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>683500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>512500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>772500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>191000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>435700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>733200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>601300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>100900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>168200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>432900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>466700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>335200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>206500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>663000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>472800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>857000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>475500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>872800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>480500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>784000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>377100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>333200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>539400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>349100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-37300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>424100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>280700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>341000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>221000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>89500</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>263200</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,8 +9910,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9734,8 +9955,8 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9812,8 +10033,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-682300</v>
+      </c>
+      <c r="E94" s="3">
         <v>471100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>84600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1049800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-751100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-499400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-280300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1496900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-979200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-304500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-313500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-327900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2496600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-684700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1234100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-826500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-551600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-403900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-161400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-773300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>118400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-463100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-249900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-327300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1727600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-530300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-649900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-261800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2077000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-616000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-472300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-642400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1421900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-704700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>92400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-252400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>37500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-28900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-190300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-149800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>17600</v>
+        <v>16900</v>
       </c>
       <c r="E96" s="3">
         <v>17600</v>
       </c>
       <c r="F96" s="3">
+        <v>17600</v>
+      </c>
+      <c r="G96" s="3">
         <v>18500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>19200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>19500</v>
-      </c>
-      <c r="I96" s="3">
-        <v>20000</v>
       </c>
       <c r="J96" s="3">
         <v>20000</v>
       </c>
       <c r="K96" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L96" s="3">
         <v>20400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>20500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>19900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>19200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>19400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>16600</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-16100</v>
       </c>
       <c r="R96" s="3">
         <v>-16100</v>
       </c>
       <c r="S96" s="3">
-        <v>-16200</v>
+        <v>-16100</v>
       </c>
       <c r="T96" s="3">
         <v>-16200</v>
       </c>
       <c r="U96" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="V96" s="3">
         <v>-16100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-16700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-35000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-17800</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-17700</v>
       </c>
       <c r="Z96" s="3">
         <v>-17700</v>
       </c>
       <c r="AA96" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-33100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-15400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-14800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-15100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-29400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-14500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-13200</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-13100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-26500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-13200</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-12700</v>
       </c>
       <c r="AL96" s="3">
         <v>-12700</v>
       </c>
       <c r="AM96" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-25900</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-13000</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-12700</v>
       </c>
       <c r="AP96" s="3">
         <v>-12700</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-12700</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-424500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1318300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-522300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-261000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-917500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>290400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-376000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-57800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-209200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-644600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>484500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-197700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2185500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>116300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>500400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>18600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>272800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-66500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>145400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-48100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-399700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-193600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>32900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-45300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>677600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-429600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>287100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-23200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>856200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>152500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>795500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>8600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>262200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>26900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>284900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-74000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-182000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-160800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>24200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-64300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E101" s="3">
         <v>7500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-18900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>10300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>5000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>12700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>12900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>6200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>12700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>12900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>6200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-900</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>3400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>5200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>4100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>5500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-260700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-168300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>29600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>272900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-204100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-43800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>103700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-54200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>20400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-270800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>681600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>251900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-119800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-130600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-193900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-165000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-296000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>418300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-349000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>52900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-450200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>449400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>101500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-193200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-482900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>507800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>200600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-437300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-86600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>654900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-95400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-813100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-713600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>780000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-41600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>202000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>32900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-72200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>37800</v>
       </c>
     </row>
